--- a/_105_Armors.xlsx
+++ b/_105_Armors.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8DE912-C845-4118-9B78-6E484E18E340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C7853F-FD63-49E1-83B6-8D3A0CBA4ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
   <si>
     <t>key</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -74,8 +74,24 @@
     <t>Shirt</t>
   </si>
   <si>
-    <t>tier</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>grade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EGrade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -149,13 +165,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,13 +454,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:F54"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="34" width="12.5703125" style="4" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="34" width="12.5625" style="4" customWidth="1"/>
+    <col min="35" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -464,12 +480,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -484,12 +500,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>1050001</v>
       </c>
-      <c r="B4" s="2">
-        <v>1</v>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C4" s="2">
         <v>9030001</v>
@@ -504,12 +520,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>1050002</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C5" s="3">
         <v>9030002</v>
@@ -524,12 +540,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>1050003</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C6" s="2">
         <v>9030003</v>
@@ -544,12 +560,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>1050004</v>
       </c>
-      <c r="B7" s="3">
-        <v>1</v>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C7" s="3">
         <v>9030004</v>
@@ -564,12 +580,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A8" s="2">
         <v>1050005</v>
       </c>
-      <c r="B8" s="2">
-        <v>2</v>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C8" s="2">
         <v>9030003</v>
@@ -584,12 +600,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
         <v>1050006</v>
       </c>
-      <c r="B9" s="3">
-        <v>2</v>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>9030004</v>
@@ -604,51 +620,51 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="11" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="13" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="11" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_105_Armors.xlsx
+++ b/_105_Armors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C7853F-FD63-49E1-83B6-8D3A0CBA4ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E45284-352C-4D85-AD82-CEA87821788D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17970" yWindow="1990" windowWidth="21600" windowHeight="11330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>key</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -91,6 +91,14 @@
   </si>
   <si>
     <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -453,14 +461,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F54"/>
+  <dimension ref="A2:G54"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="34" width="12.5625" style="4" customWidth="1"/>
-    <col min="35" max="16384" width="9.125" style="4"/>
+    <col min="1" max="35" width="12.5625" style="4" customWidth="1"/>
+    <col min="36" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,16 +479,19 @@
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -491,16 +502,19 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>1050001</v>
       </c>
@@ -508,19 +522,22 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>9030001</v>
+        <v>9060001</v>
       </c>
       <c r="D4" s="2">
+        <v>9060002</v>
+      </c>
+      <c r="E4" s="2">
         <v>1010001</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>1050002</v>
       </c>
@@ -528,19 +545,22 @@
         <v>16</v>
       </c>
       <c r="C5" s="3">
-        <v>9030002</v>
+        <v>9060003</v>
       </c>
       <c r="D5" s="3">
+        <v>9060004</v>
+      </c>
+      <c r="E5" s="3">
         <v>1010001</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>1050003</v>
       </c>
@@ -548,19 +568,22 @@
         <v>16</v>
       </c>
       <c r="C6" s="2">
-        <v>9030003</v>
+        <v>9060005</v>
       </c>
       <c r="D6" s="2">
+        <v>9060006</v>
+      </c>
+      <c r="E6" s="2">
         <v>1010001</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>1050004</v>
       </c>
@@ -568,19 +591,22 @@
         <v>16</v>
       </c>
       <c r="C7" s="3">
-        <v>9030004</v>
+        <v>9060007</v>
       </c>
       <c r="D7" s="3">
+        <v>9060008</v>
+      </c>
+      <c r="E7" s="3">
         <v>1010001</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A8" s="2">
         <v>1050005</v>
       </c>
@@ -588,19 +614,22 @@
         <v>15</v>
       </c>
       <c r="C8" s="2">
-        <v>9030003</v>
+        <v>9060009</v>
       </c>
       <c r="D8" s="2">
+        <v>9060010</v>
+      </c>
+      <c r="E8" s="2">
         <v>1010001</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
         <v>1050006</v>
       </c>
@@ -608,25 +637,28 @@
         <v>14</v>
       </c>
       <c r="C9" s="3">
-        <v>9030004</v>
+        <v>9060011</v>
       </c>
       <c r="D9" s="3">
+        <v>9060012</v>
+      </c>
+      <c r="E9" s="3">
         <v>1010001</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="11" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="13" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="15" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="11" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
     <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
